--- a/신고신저가_20260827.xlsx
+++ b/신고신저가_20260827.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 미국 지수는 사실상 제자리걸음이었지만 그 안에서는 반도체가 빠지고 헬스케어·금융·산업재가 신고가 자리를 채웠다. 중화권에서는 은행과 보험이 신고가를 거의 독식했다. 두 시장 모두 이익이 빠르게 늘어나는 자산이 아니라 지금 현금이 나오는 자산으로 돈이 옮겨간 하루였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/26): 지수가 멈춰 선 날일수록 안쪽 손바뀜을 봐야 한다. 3대 지수가 모두 0.2퍼센트 이내로 끝났는데 신고가는 51종, 신저가는 13종이 나왔다. 헬스케어와 금융이 각각 여덟 종목씩 신고가를 내며 강세를 끌었고, 반대로 전자·반도체는 신고가 없이 신저가만 세 종목이 나왔다. 스머커가 가이던스 상향으로 4.3퍼센트 오르며 신고가에 올라선 반면 나이키는 투자의견 하향에 밀려 신저가로 내려갔고, 글로벌파운드리도 성숙공정 수요 부진 속에 신저가에 합류했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/26): 제약과 금이 함께 끌어올린 신고가 장세였다. 신고가 15종에 신저가는 한 종에 그쳤고, 헬스케어와 소프트웨어가 각각 세 종목으로 가장 두꺼웠다. 다이이치산쿄와 다케다가 나란히 신고가에 올랐는데 다케다는 증권사 목표주가 상향이 붙었고 다이이치산쿄는 뚜렷한 개별 재료 없이 섹터 수급으로 밀려 올라간 것으로 보인다. 스미토모금속광산은 금값이 온스당 4,700달러에 근접하며 3개월 최고 수준을 회복한 데 힘입어 2.9퍼센트 올랐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/26): 국유은행과 바이오가 같은 날 신고가에 오른 조합이 눈에 띈다. 항셍이 0.6퍼센트, 항셍테크가 0.8퍼센트 올랐고 신고가는 9종, 신저가는 2종이었다. 금융과 헬스케어가 각각 세 종목으로 강세를 갈랐는데, 공상은행과 중국은행은 본토 자금 유입에 따른 고배당 매력이 이유였고 이노벤트바이오는 상반기 매출이 45퍼센트 늘며 9.7퍼센트 급등했다. 반면 창청자동차는 상반기 순이익이 61퍼센트 줄어든 것이 확인되며 신저가로 내려앉았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/26): 신고가가 사실상 은행·보험 한 업종에서만 나왔다. 상해종합이 0.6퍼센트, CSI300이 0.9퍼센트 오른 가운데 신고가 7종 중 5종이 금융이었고, 그중 넷이 은행과 보험이다. 증권 ETF가 2.7퍼센트, 유색금속 ETF가 2.5퍼센트로 하루 상승률 상위에 섰다. 반대편에서는 기계·설비가 신저가 두 종목으로 유일한 약세 업종이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①미국 전자·반도체가 신저가만 내는 흐름이 이어지는지 — 지수가 버티는 동안 이 업종만 빠지면 지수 방어력 자체가 얇아진다. ②중화권 은행주 랠리가 다음 주 발표될 상반기 실적에서 순이자마진 악화를 확인하고도 계속되는지. ③금값이 4,700달러선을 지키는지 — 이게 스미토모금속광산을 포함한 광산주 신고가의 전제다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 중국A 신고가 7종 중 5종이 금융이었고 홍콩도 신고가의 3분의 1이 국유은행이었는데, 이 랠리를 만든 것은 은행의 이익이 아니다. 중국 국채금리가 낮게 눌려 있어 예정이율을 약속해둔 보험사가 채권만으로는 부채를 감당하지 못하고, 배당수익률이 높은 은행주를 채권 대체재로 사들이는 흐름이 배경이다. 그러니까 주가를 밀어올린 것은 이익이 늘어서가 아니라 그 배당을 할인하는 요구수익률이 내려갔기 때문이고, 경로가 이익이 아니라 멀티플 쪽이다. 선행 PER 6.4배·PBR 0.9배라는 값이 그 증거로, 성장을 산 가격이 아니라 배당을 산 가격이다. 장쑤은행이나 상하이농촌상업은행 같은 지역은행이 대형 국유은행보다 앞서 나가는 것도 배당수익률이 더 높아 같은 자금에 더 크게 반응하기 때문으로 보인다(추정). 같은 힘이 반대편에서는 항셍테크를 52주 범위의 아래에서 15퍼센트 지점에 묶어두는데, 이익이 먼 미래에 있는 자산은 애초에 이 자금의 매수 대상이 아니기 때문이다. 이 로직이 맞는지는 은행들의 3분기 순이자마진으로 확인할 수 있다 — 마진이 깎이는데도 주가가 오른다면 멀티플 경로가 맞다는 뜻이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 미국·일본·홍콩·중국 모두 2026-08-26 현지 마감분이며, 미국분은 한국시간 오늘 새벽 5시에 끝난 세션이다. 다만 지수 시트의 닛케이225만 8월 25일 종가로 하루 지연돼 들어와 있어 본문의 일본 지수 언급은 생략했다. 섹터 ETF 시세는 44종 전부 정상 수집됐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7675.7</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>-0.42</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>3.32</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>2.07</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>12.13</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26130.2</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.08</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>5.04</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>12.43</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6742.74</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>0.68</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>-1.85</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-14.08</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>60</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>65856.42999999999</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>-2.38</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>1.93</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>1.32</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>30.82</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3912.52</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.59</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>0.46</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-4.54</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>-1.42</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4590.79</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.85</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>0.47</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-6.58</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>-0.85</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25652.97</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.62</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>1.35</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>1.28</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>0.09</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4626.15</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>-1.19</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>-2.21</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-5.73</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-16.13</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1762,7 @@
       <c r="F16" t="n">
         <v>-3</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1963,7 +2045,7 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2004,7 +2086,7 @@
       <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2125,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2084,7 +2166,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2123,7 +2205,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2162,7 +2244,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2203,7 +2285,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2242,7 +2324,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2283,7 +2365,7 @@
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2322,7 +2404,7 @@
       <c r="F32" t="n">
         <v>-1</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2759,7 +2841,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2798,7 +2880,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2837,7 +2919,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2876,7 +2958,7 @@
       <c r="F46" t="n">
         <v>-1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2917,7 +2999,7 @@
       <c r="F47" t="n">
         <v>-1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3393,7 +3475,7 @@
       <c r="F59" t="n">
         <v>5</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3434,7 +3516,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3473,7 +3555,7 @@
       <c r="F61" t="n">
         <v>-2</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4183,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4228,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4338,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.6퍼센트로 버텼지만 반도체는 신저가 3종. 1M +6.9퍼센트 상승분의 되돌림 구간으로 추정</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4414,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.0퍼센트인데 신고가는 8종으로 최다. 대형주가 끌어내리고 중소형이 신고가를 낸 갈림</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4490,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1D는 -0.1퍼센트로 보합이나 신고가 8종에 순강도 +7. 3M +13.7퍼센트로 추세는 여전히 위</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4566,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.7퍼센트. 나이키가 투자의견 하향에 신저가로 내려가며 소비재 심리를 눌렀다</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4642,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.5퍼센트로 약보합. 신고가 2종에 신저가는 없어 순강도는 소폭 플러스 유지</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4718,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.1퍼센트로 미국 섹터 중 1위. 플로우서브·링컨일렉트릭 등 기계주가 신고가를 채웠다</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4794,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.3퍼센트로 지수는 눌렸지만 스머커가 가이던스 상향에 4.3퍼센트 올라 신고가</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4870,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.6퍼센트, 1M +8.4퍼센트로 강세 지속. 셰니에어·플레인스가 나란히 신고가에 합류</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>8.4</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4946,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.5퍼센트 반등했으나 1M -4.4퍼센트로 여전히 부진. 신고가·신저가 모두 없음</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5022,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.2퍼센트, 1주 +2.2퍼센트로 미국 내 주간 1위. 비철·소재 3종이 신고가</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5098,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.6퍼센트, 1M -2.0퍼센트. 금리가 다시 올라 부동산은 매수세가 붙지 못했다</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5174,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>11.6</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5246,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5318,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>14</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5390,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5462,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>11</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5534,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5606,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-7.4</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>51.6</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5678,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>8</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5750,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>32.4</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5822,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>15.1</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5894,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>13</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5966,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6038,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6110,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6182,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>46.4</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6254,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>11.6</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6326,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6398,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6470,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6542,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-15.9</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6610,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.9퍼센트 반등했으나 3M -11.3퍼센트. 신고가 없이 낙폭 되돌림 수준으로 추정</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-11.3</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>38.9</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6686,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.6퍼센트. 3M -12.8퍼센트로 기술주 전반이 자금 유출 구간에 머물러 있다</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6762,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.4퍼센트로 약한 반등. 1M +5.8퍼센트지만 3M -18.0퍼센트로 낙폭이 여전히 깊다</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-18</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>33.1</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6838,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.2퍼센트. 3M -18.3퍼센트로 부진하나 최근 한 달은 플러스로 돌아섰다</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6910,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.5퍼센트. 3M -18.1퍼센트로 방산은 여전히 소외, 기계·설비 신저가 2종과 같은 방향</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-18.1</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-19.8</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6986,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.6퍼센트로 반등했으나 3M -24.6퍼센트로 A주 섹터 중 최하위. 공급과잉 부담 지속 추정</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-24.6</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-11.5</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7058,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.2퍼센트로 사실상 제자리. 소비 회복 신호가 아직 주가에 잡히지 않는다</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-21.1</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7134,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.0퍼센트, 3M +8.9퍼센트. 신고가 4종을 배출한 오늘 A주의 주력 업종</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7210,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>1D +2.5퍼센트, 1M +12.0퍼센트로 A주 상위. 금값 4,700달러 근접이 직접 재료</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7286,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.3퍼센트, 1M +5.8퍼센트. 베이커의 홍콩 신고가와 같은 방향의 중개·부동산 온기</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-18.2</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>11</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7362,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>1D +2.7퍼센트로 A주 1위. 은행·보험 신고가 랠리에 증권주가 거래대금 기대로 따라붙었다</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.5</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7438,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.3퍼센트지만 3M +14.3퍼센트로 A주 최상위. 홍콩 바이오 강세와 같은 흐름</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>14.3</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7514,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.2퍼센트, 1M -1.2퍼센트. 소비는 이번 금융주 랠리에서 비켜서 있다</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-16.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7582,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.5"/>
@@ -7366,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-3"/>
@@ -7378,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-5.4"/>
@@ -7390,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-24.6"/>
@@ -7402,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.1"/>
@@ -7414,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,7 +7816,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7637,14 +7865,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 브로드컴(반도체·AI칩): 마벨의 구글 커스텀칩 수주 확대로 경쟁 우려 지속</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7697,14 +7925,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 비자(카드 결제망): 분기 매출 14% 증가 여진에 피퍼샌들러 목표가 430달러 상향, 3% 급등 신고가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7753,15 +7981,15 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7803,10 +8031,10 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7855,10 +8083,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7907,15 +8135,15 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7957,10 +8185,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>TJX컴퍼니스(오프프라이스 의류 유통): 분기 실적은 상회했으나 가이던스가 보수적</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8013,14 +8245,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 스코샤뱅크(캐나다계 은행): 3분기 순익 사상최대, ROE 목표치 상회</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8073,14 +8305,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) 프리포트맥모란(구리 채굴): 구리 강세 지속, 실물자산 선호 흐름</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8129,19 +8361,19 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 스포티파이(음악 스트리밍): 자사주매입 22억달러 확대·구독자 호조</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8185,15 +8417,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8235,10 +8467,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8287,15 +8519,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8339,15 +8571,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8391,10 +8623,10 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8443,10 +8675,10 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8495,14 +8727,14 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr">
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>(전일) 카바나(중고차 온라인 유통): 고베타 위험선호 로테이션, 지분 우려 완화</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8555,15 +8787,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>도이체방크(독일 상업·투자은행): 5억유로 자사주 매입 개시, 분기 실적 호조 지속</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8607,15 +8843,19 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>셰니에어에너지(LNG 액화·수출 터미널): EBITDA 가이던스 상향 여진에 에너지 섹터 강세 가세</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8663,10 +8903,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>나이키(스포츠화·의류): 대형 투자은행이 투자의견 비중축소로 하향, 재건 비용 우려</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8715,10 +8959,10 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8771,10 +9015,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8823,15 +9067,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8873,15 +9117,19 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>페로비알(유료도로·공항 인프라 운영): 특별한 뉴스 없음(개별 약세 지속)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8929,10 +9177,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8981,15 +9229,15 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9037,10 +9285,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9089,14 +9337,14 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>(전일) (프레스티지 화장품) 분기 EPS 서프라이즈와 중국 매출 회복에 목표가 줄상향</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9149,15 +9397,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9201,10 +9449,10 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9257,19 +9505,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="7" t="inlineStr">
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>(전일) (유전체 시퀀싱 장비) 2분기 매출 서프라이즈 여진에 신고가 지속</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9313,15 +9561,15 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9369,15 +9617,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9421,15 +9669,15 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9473,10 +9721,14 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>글로벌파운드리(성숙공정 반도체 파운드리): 특별한 뉴스 없음(성숙공정 수요 부진 지속)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9529,10 +9781,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9581,10 +9833,10 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9633,14 +9885,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>(전일) 페덱스프레이트(페덱스에서 분할한 소량화물 운송): 화물 업황 약세로 JB헌트와 동반 신저가</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9689,15 +9941,15 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9745,15 +9997,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="7" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9801,10 +10053,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>플레인스올아메리칸(원유 파이프라인 MLP): 개별 재료 없음, 에너지·산업재 섹터 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9853,10 +10109,10 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9905,15 +10161,15 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9961,15 +10217,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10011,15 +10267,15 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10063,10 +10319,14 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>링컨일렉트릭(산업용 용접장비): 개별 재료 없음, 산업재 섹터 전반 랠리에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10119,10 +10379,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10173,15 +10433,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10229,15 +10489,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10283,15 +10543,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>스머커(잼·커피·펫푸드 식품): 분기 매출·이익 서프라이즈에 연간 이익 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10335,10 +10599,10 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10387,15 +10651,15 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10439,10 +10703,10 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10495,10 +10759,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10545,15 +10809,15 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10597,10 +10861,10 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10651,14 +10915,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="7" t="inlineStr">
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>(전일) 딕스스포팅굿즈(스포츠용품 유통): 2분기 실적쇼크·가이던스 대폭 하향(풋라커 부진)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10707,15 +10971,15 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10759,15 +11023,19 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>TFI인터내셔널(북미 화물운송·물류): 특별한 뉴스 없음(운임 부진 흐름 지속)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10811,15 +11079,15 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10863,15 +11131,15 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10915,10 +11183,14 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>플로우서브(산업용 펌프·밸브): 개별 재료 없음, 산업재 섹터 전반 랠리에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10971,15 +11243,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11023,7 +11295,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N65"/>
@@ -11129,7 +11401,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11176,19 +11448,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 패스트리테일링(유니클로 모기업): 개별 악재 없음, 지수 기여 상위주 차익실현</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11236,10 +11508,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>리크루트홀딩스(구인구직 플랫폼·인재파견): 증권사 두 곳이 목표주가를 2만엔 안팎으로 상향</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11288,14 +11564,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 이토추상사(종합상사): 3000억엔 자사주매입·사상최대 순이익 모멘텀 지속, 상사 섹터 강세</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11346,14 +11622,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) (일본 통신 1위 NTT그룹) 방어주 선호 속 매수세로 신고가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11406,19 +11682,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 소프트뱅크(통신): NTT·KDDI와 함께 통신주 동반 강세, 연초래 고가권 지속</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11460,15 +11736,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>다케다약품공업(제약): 증권사들이 목표주가를 7,100~7,600엔으로 상향, 파이프라인 기대</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11512,15 +11792,15 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11564,15 +11844,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>다이이치산쿄(항암 ADC 중심 제약): 개별 재료 없음, 제약 섹터 수급 강세 추정</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11614,10 +11898,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11668,14 +11952,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) (포털·핀테크 플랫폼) 페이페이 결제액 34.9% 성장 등 실적 호조 지속</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11726,19 +12010,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 반다이남코(게임·완구 지식재산): 1분기 영업이익 33퍼센트 증가 서프라이즈 여진</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11782,10 +12066,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>스미토모금속광산(금·구리 채굴 비철금속): 금값 온스당 4,700달러 근접, 3개월 최고 수준 회복</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11832,14 +12120,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 간사이전력(관서지역 전력): 기업용 전기요금 인상 발표 후 수익성 개선 기대</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11888,19 +12176,19 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) (증권·은행 겸영 금융지주) 금리 상승 수혜 기대에 신고가</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11946,15 +12234,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>젠쇼홀딩스(스키야·하마즈시 외식 체인): 초밥 사업 호조로 연매출 11%·순이익 17% 증가</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11996,7 +12288,7 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N17"/>
@@ -12102,12 +12394,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12153,15 +12445,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>공상은행(중국 최대 국유 상업은행): 본토 자금 유입 지속에 고배당 매력 부각</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12207,10 +12503,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>중국은행(중국 4대 국유 상업은행): 본토 자금 유입과 배당 매력에 은행주 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12257,14 +12557,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 시노펙 H주(중국 최대 정유·화학): 상반기 순이익 19% 증가 실적 호조에 5.9% 급등</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12315,19 +12615,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 우시바이오로직스(바이오의약 위탁생산): 항체약물접합체 호황에 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12371,15 +12671,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>이노벤트바이오(중국 항암 바이오신약): 상반기 매출 45% 급증, 기술수출 기대 겹쳐 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12423,15 +12727,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>베이커(중국 주택 중개 플랫폼): 2분기 순이익 두 배 증가 실적 발표 후 매수세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12477,10 +12785,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>창청자동차(중국 SUV·픽업 완성차): 상반기 순이익 61% 급감, 마진 훼손 우려로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12529,19 +12841,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 우시XDC(항체약물접합체 위탁생산): 실적 가이던스 상향·수주잔고 급증</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12583,10 +12895,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>시노바이오파마(중국 제네릭·신약 제약): 기술수출 기대로 신약 섹터 전반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12631,14 +12947,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 톈수즈신(중국 AI 가속칩 설계): 알리바바 102억달러 유상증자發 AI 밸류체인 동반 급락, 10.6% 하락</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12681,7 +12997,7 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 밍밍헌망(중국 간식 소매체인): 특별한 뉴스 없음(수급 흐름 추정)</t>
         </is>
@@ -12791,12 +13107,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12838,10 +13154,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>핑안보험(중국 최대 민영 보험·금융그룹): 보험자금의 저평가 배당주 확대 흐름에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12892,14 +13212,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 중신은행 A주(중국 상업은행): 기술주 급락 속 저평가·고배당 선호로 자금이동, 장중 사상최고가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12948,19 +13268,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 위수커지(사족보행 로봇 제조): 상장 초기 차익실현 급증, 시초가 대비 45% 넘게 반락</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13004,15 +13324,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>핑안은행(핑안그룹 계열 전국구 상업은행): 개별 재료 없음, 금융 섹터 전반 강세에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13058,10 +13382,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>장쑤은행(장쑤성 도시상업은행): 전 거래일 사상 최고가에 이어 연속 신고가, 은행주 랠리 주도</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13110,14 +13438,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 마이루이의료(의료기기): 특별한 뉴스 없음, 의료기기 섹터 수급 흐름 추정</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13168,14 +13496,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 쑹파세라믹(도자기 식기): 특별한 뉴스 없음, 소형 테마주 수급 쏠림 추정</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13224,19 +13552,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) 헝리유압(굴착기용 유압부품): 특별한 뉴스 없음, 건설기계 섹터 조정 흐름 추정</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13278,10 +13606,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>상하이농촌상업은행(상하이 지역 상업은행): 낮은 PBR·높은 배당에 보험자금 유입, 연속 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13330,7 +13662,7 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 저장신허(비타민·정밀화학 생산): 개별 악재 미확인, 화학·성장주 동반 약세 추정</t>
         </is>
